--- a/Mapeo_CI_Proyectos_a_2025_-_2026.xlsx
+++ b/Mapeo_CI_Proyectos_a_2025_-_2026.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="I2" s="11" t="inlineStr">
         <is>
-          <t>PROYECTO EDUCACIÓN Y PROTECCIÓN EN EMERGENCIAS</t>
+          <t>Proyecto Educación y Protección en Emergencias</t>
         </is>
       </c>
       <c r="J2" s="7" t="n">
@@ -704,18 +704,18 @@
       </c>
       <c r="N2" s="11" t="inlineStr">
         <is>
-          <t>educación_innovacion,otro</t>
+          <t>Educación Innovación, Otro</t>
         </is>
       </c>
       <c r="O2" s="11" t="n"/>
       <c r="P2" s="11" t="inlineStr">
         <is>
-          <t>EN EL MARCO DE LA IMPLEMENTACIÓN DE ESTE PROYECTO ACOMPAÑAMOS PROCESOS PARA LA PROTECCIÓN DE LOS NIÑOS, NIÑAS Y ADOLESCENTES A TRAVÉS DE ACOMPAÑAMIENTO PSICOSOCIAL, JURÍDICO Y EDUCATIVO</t>
+          <t>En el marco de la implementación de este proyecto acompañamos procesos para la protección de los niños, niñas y adolescentes a través de acompañamiento psicosocial, jurídico y educativo</t>
         </is>
       </c>
       <c r="Q2" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acompañamiento psico-social grupal e individual./Desarrollo de acciones en Educación, acompañamiento a las IE participantes y la entrega de ayudas tangibles como kits escolares./Desarrollo de la campaña "No aguanta Hacernos Daño" </t>
+          <t>Acompañamiento psico-social grupal e individual./Desarrollo de acciones en Educación, acompañamiento a las IE participantes y la entrega de ayudas tangibles como kits escolares./Desarrollo de la campaña "No aguanta Hacernos Daño"</t>
         </is>
       </c>
       <c r="R2" s="11" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="S2" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">El alcance del proyecto es integral, abarcando la protección psicosocial y jurídica, así como la educación flexible y la recuperación escolar, con acciones directas en varias comunidades del territorio. </t>
+          <t>El alcance del proyecto es integral, abarcando la protección psicosocial y jurídica, así como la educación flexible y la recuperación escolar, con acciones directas en varias comunidades del territorio.</t>
         </is>
       </c>
       <c r="T2" s="11" t="inlineStr">
@@ -736,7 +736,7 @@
       <c r="U2" s="11" t="n"/>
       <c r="V2" s="11" t="inlineStr">
         <is>
-          <t>san_jose_del_guaviare,el_retorno,miraflores</t>
+          <t>San José del Guaviare, El Retorno, Miraflores</t>
         </is>
       </c>
       <c r="W2" s="11" t="inlineStr">
@@ -752,7 +752,7 @@
       <c r="Y2" s="11" t="n"/>
       <c r="Z2" s="11" t="inlineStr">
         <is>
-          <t>ninos,jovenes,mujeres,hombres,adultos</t>
+          <t>Niños, Jóvenes, Mujeres, Hombres, Adultos</t>
         </is>
       </c>
       <c r="AA2" s="11" t="n"/>
@@ -785,7 +785,7 @@
       </c>
       <c r="AQ2" s="11" t="inlineStr">
         <is>
-          <t>ods3,ods4,ods5,ods16</t>
+          <t>3, 4, 5, 16</t>
         </is>
       </c>
       <c r="AR2" s="11" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="I3" s="11" t="inlineStr">
         <is>
-          <t>Áreas Protegidas y Paz -  AP&amp;P</t>
+          <t>Áreas Protegidas y Paz - AP&amp;P</t>
         </is>
       </c>
       <c r="J3" s="7" t="n">
@@ -832,13 +832,13 @@
       <c r="M3" s="11" t="n"/>
       <c r="N3" s="11" t="inlineStr">
         <is>
-          <t>Agropecuario,Ambiental,Socioeconómico</t>
+          <t>Agropecuario, Ambiental, Socioeconómico</t>
         </is>
       </c>
       <c r="O3" s="11" t="n"/>
       <c r="P3" s="11" t="inlineStr">
         <is>
-          <t>Se reconocen los derechos a la tierra y al uso de los pequeños agricultores y se adoptan sistemas de gestión participativos, sostenibles, resilientes al  clima y basados en la naturaleza que promueven la paz territorial en el sistema de áreas protegidas..</t>
+          <t>Se reconocen los derechos a la tierra y al uso de los pequeños agricultores y se adoptan sistemas de gestión participativos, sostenibles, resilientes al clima y basados en la naturaleza que promueven la paz territorial en el sistema de áreas protegidas..</t>
         </is>
       </c>
       <c r="Q3" s="11" t="n"/>
@@ -868,7 +868,7 @@
       <c r="Y3" s="11" t="n"/>
       <c r="Z3" s="11" t="inlineStr">
         <is>
-          <t>Mujeres,Hombres,Jovenes,Adultos</t>
+          <t>Mujeres, Hombres, Jóvenes, Adultos</t>
         </is>
       </c>
       <c r="AA3" s="11" t="n"/>
@@ -936,13 +936,13 @@
       <c r="M4" s="11" t="n"/>
       <c r="N4" s="11" t="inlineStr">
         <is>
-          <t>Agropecuario,Ambiental,Socioeconómico</t>
+          <t>Agropecuario, Ambiental, Socioeconómico</t>
         </is>
       </c>
       <c r="O4" s="11" t="n"/>
       <c r="P4" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">fortalecer la gobernanza en los territorios de los Pueblos Indígenas y Comunidades Locales a través del monitoreo del Jaguar y sus presas, como herramienta para el manejo sustentable de sus territorios... </t>
+          <t>fortalecer la gobernanza en los territorios de los Pueblos Indígenas y Comunidades Locales a través del monitoreo del Jaguar y sus presas, como herramienta para el manejo sustentable de sus territorios...</t>
         </is>
       </c>
       <c r="Q4" s="11" t="n"/>
@@ -956,7 +956,7 @@
       <c r="U4" s="11" t="n"/>
       <c r="V4" s="11" t="inlineStr">
         <is>
-          <t>San_José_Del_Guaviare</t>
+          <t>San José del Guaviare</t>
         </is>
       </c>
       <c r="W4" s="11" t="inlineStr">
@@ -972,7 +972,7 @@
       <c r="Y4" s="11" t="n"/>
       <c r="Z4" s="11" t="inlineStr">
         <is>
-          <t>Mujeres,Hombres,Jovenes,Adultos,Étnicos,Afro,Desplazados</t>
+          <t>Mujeres, Hombres, Jóvenes, Adultos, Étnicos, Afro, Desplazados</t>
         </is>
       </c>
       <c r="AA4" s="11" t="n"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Hilmer  Viafara Gómez</t>
+          <t>Hilmer Viafara Gómez</t>
         </is>
       </c>
       <c r="C5" s="11" t="n"/>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>GLOBAL 2: BMZ-PT PROMOCIÓN DE COMUNIDADES RESILIENTES EN LA AMAZONÍA EN EL CONTEXTO DEL CAMBIO CLIMÁTICO Y DE LA PRESERVACIÓN DE LA BIODIVERSIDAD, COLOMBIA 2023- 2026</t>
+          <t>Global 2: BMZ-PT Promoción de Comunidades Resilientes en la Amazonía en el Contexto del Cambio Climático y de la Preservación de la Biodiversidad, Colombia 2023- 2026</t>
         </is>
       </c>
       <c r="J5" s="7" t="n">
@@ -1040,7 +1040,7 @@
       <c r="M5" s="11" t="n"/>
       <c r="N5" s="11" t="inlineStr">
         <is>
-          <t>Agropecuario,Ambiental,Socioeconómico</t>
+          <t>Agropecuario, Ambiental, Socioeconómico</t>
         </is>
       </c>
       <c r="O5" s="11" t="n"/>
@@ -1076,7 +1076,7 @@
       <c r="Y5" s="11" t="n"/>
       <c r="Z5" s="11" t="inlineStr">
         <is>
-          <t>Mujeres,Hombres,Jovenes,Adultos,Étnicos,Afro</t>
+          <t>Mujeres, Hombres, Jóvenes, Adultos, Étnicos, Afro</t>
         </is>
       </c>
       <c r="AA5" s="11" t="n"/>
@@ -1144,7 +1144,7 @@
       <c r="M6" s="11" t="n"/>
       <c r="N6" s="11" t="inlineStr">
         <is>
-          <t>Agropecuario,Ambiental,Socioeconómico</t>
+          <t>Agropecuario, Ambiental, Socioeconómico</t>
         </is>
       </c>
       <c r="O6" s="11" t="n"/>
@@ -1164,7 +1164,7 @@
       <c r="U6" s="11" t="n"/>
       <c r="V6" s="11" t="inlineStr">
         <is>
-          <t>San_José_Del_Guaviare,El_Retorno,Calamar</t>
+          <t>San José del Guaviare, El Retorno, Calamar</t>
         </is>
       </c>
       <c r="W6" s="11" t="inlineStr">
@@ -1180,7 +1180,7 @@
       <c r="Y6" s="11" t="n"/>
       <c r="Z6" s="11" t="inlineStr">
         <is>
-          <t>Mujeres,Hombres,Jovenes,Adultos,Afro,Desplazados</t>
+          <t>Mujeres, Hombres, Jóvenes, Adultos, Afro, Desplazados</t>
         </is>
       </c>
       <c r="AA6" s="11" t="n"/>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>PEDRO ENRIQUE SALAZAR CASTILLO</t>
+          <t>Pedro Enrique Salazar Castillo</t>
         </is>
       </c>
       <c r="C7" s="11" t="n"/>
@@ -1254,7 +1254,7 @@
       <c r="O7" s="11" t="n"/>
       <c r="P7" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. manejo de áreas protegidas y sostenibilidad financiera. 2. Gobernanza, manejo y monitoreo de los bosques. 3. programas sostenibles para el manejo sostenible del paisaje. 4. </t>
+          <t>1. manejo de áreas protegidas y sostenibilidad financiera. 2. Gobernanza, manejo y monitoreo de los bosques. 3. programas sostenibles para el manejo sostenible del paisaje. 4.</t>
         </is>
       </c>
       <c r="Q7" s="11" t="n"/>
@@ -1268,7 +1268,7 @@
       <c r="U7" s="11" t="n"/>
       <c r="V7" s="11" t="inlineStr">
         <is>
-          <t>San_José_Del_Guaviare,El_Retorno,Calamar,Miraflores</t>
+          <t>San José del Guaviare, El Retorno, Calamar, Miraflores</t>
         </is>
       </c>
       <c r="W7" s="11" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="Z7" s="11" t="inlineStr">
         <is>
-          <t>Niños,Niñas,Mujeres,Hombres,Jovenes,Adultos,Étnicos,Afro,Desplazados,Discapacitados,Reincorporados,LGBTIQ+</t>
+          <t>Niños, Niñas, Mujeres, Hombres, Jóvenes, Adultos, Étnicos, Afro, Desplazados, Discapacitados, Reincorporados, LGBTIQ+</t>
         </is>
       </c>
       <c r="AA7" s="11" t="n"/>
@@ -1380,7 +1380,7 @@
       <c r="U8" s="11" t="n"/>
       <c r="V8" s="11" t="inlineStr">
         <is>
-          <t>San_José_Del_Guaviare,El_Retorno,Calamar,Miraflores</t>
+          <t>San José del Guaviare, El Retorno, Calamar, Miraflores</t>
         </is>
       </c>
       <c r="W8" s="11" t="inlineStr">
@@ -1396,7 +1396,7 @@
       <c r="Y8" s="11" t="n"/>
       <c r="Z8" s="11" t="inlineStr">
         <is>
-          <t>Mujeres,Hombres,Jovenes,Adultos,Étnicos</t>
+          <t>Mujeres, Hombres, Jóvenes, Adultos, Étnicos</t>
         </is>
       </c>
       <c r="AA8" s="11" t="n"/>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="P9" s="11" t="inlineStr">
         <is>
-          <t>Fortalecimiento de  capacidades de la sociedad civil para prevenir, proteger, observar e incidir en las políticas estatales de la protección y atención de niños, niñas, adolescentes y jóvenes.</t>
+          <t>Fortalecimiento de capacidades de la sociedad civil para prevenir, proteger, observar e incidir en las políticas estatales de la protección y atención de niños, niñas, adolescentes y jóvenes.</t>
         </is>
       </c>
       <c r="Q9" s="11" t="n"/>
@@ -1488,7 +1488,7 @@
       <c r="U9" s="11" t="n"/>
       <c r="V9" s="11" t="inlineStr">
         <is>
-          <t>San_José_Del_Guaviare</t>
+          <t>San José del Guaviare</t>
         </is>
       </c>
       <c r="W9" s="11" t="inlineStr">
@@ -1504,7 +1504,7 @@
       <c r="Y9" s="11" t="n"/>
       <c r="Z9" s="11" t="inlineStr">
         <is>
-          <t>Niños,Niñas,Mujeres,Étnicos</t>
+          <t>Niños, Niñas, Mujeres, Étnicos</t>
         </is>
       </c>
       <c r="AA9" s="11" t="n"/>
@@ -1558,7 +1558,7 @@
       <c r="G10" s="11" t="n"/>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banco mundial, unodc, niras </t>
+          <t>Banco mundial, unodc, niras</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
@@ -1576,7 +1576,7 @@
       <c r="M10" s="11" t="n"/>
       <c r="N10" s="11" t="inlineStr">
         <is>
-          <t>Ambiental,Socioeconómico</t>
+          <t>Ambiental, Socioeconómico</t>
         </is>
       </c>
       <c r="O10" s="11" t="n"/>
@@ -1596,7 +1596,7 @@
       <c r="U10" s="11" t="n"/>
       <c r="V10" s="11" t="inlineStr">
         <is>
-          <t>El_Retorno,Calamar,Miraflores</t>
+          <t>El Retorno, Calamar, Miraflores</t>
         </is>
       </c>
       <c r="W10" s="11" t="inlineStr">
@@ -1612,7 +1612,7 @@
       <c r="Y10" s="11" t="n"/>
       <c r="Z10" s="11" t="inlineStr">
         <is>
-          <t>Niños,Niñas,Mujeres,Hombres,Jovenes,Adultos,Étnicos,Afro,Desplazados,Discapacitados,Reincorporados,LGBTIQ+</t>
+          <t>Niños, Niñas, Mujeres, Hombres, Jóvenes, Adultos, Étnicos, Afro, Desplazados, Discapacitados, Reincorporados, LGBTIQ+</t>
         </is>
       </c>
       <c r="AA10" s="11" t="n"/>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Iniciativa Interreligiosa Para Los Bosques Tropicales Iri-Colombia</t>
+          <t>Iniciativa Interreligiosa Para Los Bosques Tropicales Iri-Colombia</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
@@ -1704,7 +1704,7 @@
       <c r="U11" s="11" t="n"/>
       <c r="V11" s="11" t="inlineStr">
         <is>
-          <t>San_José_Del_Guaviare,El_Retorno,Calamar,Miraflores</t>
+          <t>San José del Guaviare, El Retorno, Calamar, Miraflores</t>
         </is>
       </c>
       <c r="W11" s="11" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="Z11" s="11" t="inlineStr">
         <is>
-          <t>Mujeres,Hombres,Adultos,Étnicos,Afro</t>
+          <t>Mujeres, Hombres, Adultos, Étnicos, Afro</t>
         </is>
       </c>
       <c r="AA11" s="11" t="n"/>
@@ -1796,7 +1796,7 @@
       <c r="M12" s="11" t="n"/>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>Agropecuario,Ambiental,Socioeconómico</t>
+          <t>Agropecuario, Ambiental, Socioeconómico</t>
         </is>
       </c>
       <c r="O12" s="11" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P12" s="11" t="inlineStr">
         <is>
-          <t>Contribuir a recuperar la biodiversidad y los sumideros de carbono impactados por la deforestación en el Núcleo de Desarrollo Forestal y Biodiversidad Yaguara II (En el marco del Plan Integral de Contención de la Deforestación  del Gobierno de Colombia)</t>
+          <t>Contribuir a recuperar la biodiversidad y los sumideros de carbono impactados por la deforestación en el Núcleo de Desarrollo Forestal y Biodiversidad Yaguara II (En el marco del Plan Integral de Contención de la Deforestación del Gobierno de Colombia)</t>
         </is>
       </c>
       <c r="Q12" s="11" t="n"/>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="Z12" s="11" t="inlineStr">
         <is>
-          <t>Mujeres,Jovenes,Adultos,Étnicos,Desplazados</t>
+          <t>Mujeres, Jóvenes, Adultos, Étnicos, Desplazados</t>
         </is>
       </c>
       <c r="AA12" s="11" t="n"/>
@@ -1888,13 +1888,13 @@
       <c r="E13" s="11" t="n"/>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fondo Mundial para el Medio Ambiente (GEF)  </t>
+          <t>Fondo Mundial para el Medio Ambiente (GEF)</t>
         </is>
       </c>
       <c r="G13" s="11" t="n"/>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Implementado por el Banco Mundial, ejecutado por Patrimonio </t>
+          <t>Implementado por el Banco Mundial, ejecutado por Patrimonio</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
@@ -1918,7 +1918,7 @@
       <c r="O13" s="11" t="n"/>
       <c r="P13" s="11" t="inlineStr">
         <is>
-          <t>El proyecto Corazón de la Amazonia que hace parte del Programa ASL (Paisajes Sostenibles de la Amazonia) busca mejorar la gobernanza y  autonomía de comunidades indígenas y campesinas, además de promover actividades de uso sostenible de la tierra</t>
+          <t>El proyecto Corazón de la Amazonia que hace parte del Programa ASL (Paisajes Sostenibles de la Amazonia) busca mejorar la gobernanza y autonomía de comunidades indígenas y campesinas, además de promover actividades de uso sostenible de la tierra</t>
         </is>
       </c>
       <c r="Q13" s="11" t="n"/>
@@ -1932,7 +1932,7 @@
       <c r="U13" s="11" t="n"/>
       <c r="V13" s="11" t="inlineStr">
         <is>
-          <t>San_José_Del_Guaviare,Calamar</t>
+          <t>San José del Guaviare, Calamar</t>
         </is>
       </c>
       <c r="W13" s="11" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="Z13" s="11" t="inlineStr">
         <is>
-          <t>Mujeres,Hombres,Jovenes,Adultos,Étnicos</t>
+          <t>Mujeres, Hombres, Jóvenes, Adultos, Étnicos</t>
         </is>
       </c>
       <c r="AA13" s="11" t="n"/>
@@ -2044,7 +2044,7 @@
       <c r="U14" s="11" t="n"/>
       <c r="V14" s="11" t="inlineStr">
         <is>
-          <t>San_José_Del_Guaviare</t>
+          <t>San José del Guaviare</t>
         </is>
       </c>
       <c r="W14" s="11" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="Z14" s="11" t="inlineStr">
         <is>
-          <t>Mujeres,Hombres</t>
+          <t>Mujeres, Hombres</t>
         </is>
       </c>
       <c r="AA14" s="11" t="n"/>
@@ -2112,7 +2112,7 @@
       <c r="E15" s="11" t="n"/>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gobierno de Reino Unido </t>
+          <t>Gobierno de Reino Unido</t>
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
@@ -2136,7 +2136,7 @@
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>Ambiental,Socioeconómico</t>
+          <t>Ambiental, Socioeconómico</t>
         </is>
       </c>
       <c r="O15" s="11" t="n"/>
@@ -2156,7 +2156,7 @@
       <c r="U15" s="11" t="n"/>
       <c r="V15" s="11" t="inlineStr">
         <is>
-          <t>San_José_Del_Guaviare,El_Retorno,Calamar,Miraflores</t>
+          <t>San José del Guaviare, El Retorno, Calamar, Miraflores</t>
         </is>
       </c>
       <c r="W15" s="11" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="Z15" s="11" t="inlineStr">
         <is>
-          <t>Mujeres,Hombres,Étnicos</t>
+          <t>Mujeres, Hombres, Étnicos</t>
         </is>
       </c>
       <c r="AA15" s="11" t="n"/>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corazon de Amazonia GEF </t>
+          <t>Corazon de Amazonia GEF</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
@@ -2254,7 +2254,7 @@
       <c r="O16" s="11" t="n"/>
       <c r="P16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejorar la gobernanza y promover actividades de uso sostenible de las tierras, con el fin de reducir la deforestación y conservar la biodiversidad en las áreas del Proyecto. </t>
+          <t>Mejorar la gobernanza y promover actividades de uso sostenible de las tierras, con el fin de reducir la deforestación y conservar la biodiversidad en las áreas del Proyecto.</t>
         </is>
       </c>
       <c r="Q16" s="11" t="n"/>
@@ -2268,7 +2268,7 @@
       <c r="U16" s="11" t="n"/>
       <c r="V16" s="11" t="inlineStr">
         <is>
-          <t>San_José_Del_Guaviare,Calamar</t>
+          <t>San José del Guaviare, Calamar</t>
         </is>
       </c>
       <c r="W16" s="11" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="Z16" s="11" t="inlineStr">
         <is>
-          <t>Mujeres,Hombres,Jovenes,Adultos</t>
+          <t>Mujeres, Hombres, Jóvenes, Adultos</t>
         </is>
       </c>
       <c r="AA16" s="11" t="n"/>
@@ -2360,13 +2360,13 @@
       <c r="M17" s="11" t="n"/>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>Agropecuario,Socioeconómico</t>
+          <t>Agropecuario, Socioeconómico</t>
         </is>
       </c>
       <c r="O17" s="11" t="n"/>
       <c r="P17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">El proyecto contribuye a la mejora de los medios de vida sostenibles de los pequeños productores de cacao, al cumplimiento del Acuerdo de Paz y a la reducción de la presión sobre los bosques amazónicos en Caquetá, Guaviare y Putumayo.									</t>
+          <t>El proyecto contribuye a la mejora de los medios de vida sostenibles de los pequeños productores de cacao, al cumplimiento del Acuerdo de Paz y a la reducción de la presión sobre los bosques amazónicos en Caquetá, Guaviare y Putumayo.</t>
         </is>
       </c>
       <c r="Q17" s="11" t="n"/>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="Z17" s="11" t="inlineStr">
         <is>
-          <t>Mujeres,Hombres,Jovenes,Adultos,Afro,Desplazados</t>
+          <t>Mujeres, Hombres, Jóvenes, Adultos, Afro, Desplazados</t>
         </is>
       </c>
       <c r="AA17" s="11" t="n"/>
@@ -2472,13 +2472,13 @@
       <c r="M18" s="11" t="n"/>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>Ambiental,Socioeconómico,Otro</t>
+          <t>Ambiental, Socioeconómico, Otro</t>
         </is>
       </c>
       <c r="O18" s="11" t="n"/>
       <c r="P18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construir colectivamente con comunidades, organizaciones sociales y entidades territoriales propuestas de solución a los diversos retos, debilidades y problemas que enfrenta el ordenamiento, la planeación y el desarrollo territorial </t>
+          <t>Construir colectivamente con comunidades, organizaciones sociales y entidades territoriales propuestas de solución a los diversos retos, debilidades y problemas que enfrenta el ordenamiento, la planeación y el desarrollo territorial</t>
         </is>
       </c>
       <c r="Q18" s="11" t="n"/>
@@ -2492,7 +2492,7 @@
       <c r="U18" s="11" t="n"/>
       <c r="V18" s="11" t="inlineStr">
         <is>
-          <t>San_José_Del_Guaviare,El_Retorno,Calamar,Miraflores</t>
+          <t>San José del Guaviare, El Retorno, Calamar, Miraflores</t>
         </is>
       </c>
       <c r="W18" s="11" t="inlineStr">
@@ -2508,7 +2508,7 @@
       <c r="Y18" s="11" t="n"/>
       <c r="Z18" s="11" t="inlineStr">
         <is>
-          <t>Mujeres,Hombres,Étnicos,Afro</t>
+          <t>Mujeres, Hombres, Étnicos, Afro</t>
         </is>
       </c>
       <c r="AA18" s="11" t="n"/>
@@ -2556,18 +2556,18 @@
       <c r="E19" s="11" t="n"/>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>ECOPETROL - THE NATURE CONSERVANCY</t>
+          <t>Ecopetrol - The Nature Conservancy</t>
         </is>
       </c>
       <c r="G19" s="11" t="n"/>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>THE NATURE CONSERVANCY</t>
+          <t>The Nature Conservancy</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>BIOECONOMIA</t>
+          <t>Bioeconomia</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
@@ -2580,7 +2580,7 @@
       <c r="M19" s="11" t="n"/>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>Ambiental,Socioeconómico</t>
+          <t>Ambiental, Socioeconómico</t>
         </is>
       </c>
       <c r="O19" s="11" t="n"/>
@@ -2600,7 +2600,7 @@
       <c r="U19" s="11" t="n"/>
       <c r="V19" s="11" t="inlineStr">
         <is>
-          <t>San_José_Del_Guaviare,El_Retorno,Calamar,Miraflores</t>
+          <t>San José del Guaviare, El Retorno, Calamar, Miraflores</t>
         </is>
       </c>
       <c r="W19" s="11" t="inlineStr">
@@ -2616,7 +2616,7 @@
       <c r="Y19" s="11" t="n"/>
       <c r="Z19" s="11" t="inlineStr">
         <is>
-          <t>Mujeres,Hombres,Jovenes,Adultos,Étnicos,Afro,Desplazados,Discapacitados,LGBTIQ+</t>
+          <t>Mujeres, Hombres, Jóvenes, Adultos, Étnicos, Afro, Desplazados, Discapacitados, LGBTIQ+</t>
         </is>
       </c>
       <c r="AA19" s="11" t="n"/>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laura Maria Sanchez </t>
+          <t>Laura Maria Sanchez</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
@@ -2679,7 +2679,7 @@
       <c r="H20" s="11" t="n"/>
       <c r="I20" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Conectando a los no conectados: Redes comunitarias de internet como vehículo para reducir la brecha digital en zonas rurales de Colombia.</t>
+          <t>Conectando a los no conectados: Redes comunitarias de internet como vehículo para reducir la brecha digital en zonas rurales de Colombia.</t>
         </is>
       </c>
       <c r="J20" s="7" t="n">
@@ -2724,7 +2724,7 @@
       <c r="Y20" s="11" t="n"/>
       <c r="Z20" s="11" t="inlineStr">
         <is>
-          <t>Mujeres,Hombres,Jovenes,Adultos,Étnicos,Afro,Reincorporados</t>
+          <t>Mujeres, Hombres, Jóvenes, Adultos, Étnicos, Afro, Reincorporados</t>
         </is>
       </c>
       <c r="AA20" s="11" t="n"/>
@@ -2836,7 +2836,7 @@
       <c r="Y21" s="11" t="n"/>
       <c r="Z21" s="11" t="inlineStr">
         <is>
-          <t>Niños,Niñas,Mujeres,Hombres,Jovenes,Adultos,Étnicos,Afro,Desplazados,Discapacitados,Reincorporados,LGBTIQ+</t>
+          <t>Niños, Niñas, Mujeres, Hombres, Jóvenes, Adultos, Étnicos, Afro, Desplazados, Discapacitados, Reincorporados, LGBTIQ+</t>
         </is>
       </c>
       <c r="AA21" s="11" t="n"/>
@@ -2918,7 +2918,7 @@
       <c r="O22" s="11" t="n"/>
       <c r="P22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fortalecer la gestión ambiental comunitaria, por medio del fortalecimiento de las 5 líneas de acción y la promotoría campesina del corredor del jaguar Guaviare </t>
+          <t>Fortalecer la gestión ambiental comunitaria, por medio del fortalecimiento de las 5 líneas de acción y la promotoría campesina del corredor del jaguar Guaviare</t>
         </is>
       </c>
       <c r="Q22" s="11" t="n"/>
@@ -2936,7 +2936,7 @@
       <c r="U22" s="11" t="n"/>
       <c r="V22" s="11" t="inlineStr">
         <is>
-          <t>san_jose_del_guaviare</t>
+          <t>San José del Guaviare</t>
         </is>
       </c>
       <c r="W22" s="11" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="Z22" s="11" t="inlineStr">
         <is>
-          <t>ninos,ninas,mujeres,hombres,jovenes,adultos</t>
+          <t>Niños, Niñas, Mujeres, Hombres, Jóvenes, Adultos</t>
         </is>
       </c>
       <c r="AA22" s="11" t="n"/>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AQ22" s="11" t="inlineStr">
         <is>
-          <t>1,5,8,12,16</t>
+          <t>1, 5, 8, 12, 16</t>
         </is>
       </c>
       <c r="AR22" s="11" t="n"/>
@@ -3058,7 +3058,7 @@
       <c r="U23" s="11" t="n"/>
       <c r="V23" s="11" t="inlineStr">
         <is>
-          <t>san_jose_del_guaviare</t>
+          <t>San José del Guaviare</t>
         </is>
       </c>
       <c r="W23" s="11" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="Z23" s="11" t="inlineStr">
         <is>
-          <t>ninos,ninas,mujeres,hombres,jovenes,adultos,etnicos,afro</t>
+          <t>Niños, Niñas, Mujeres, Hombres, Jóvenes, Adultos, Étnicos, Afro</t>
         </is>
       </c>
       <c r="AA23" s="11" t="n"/>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="AQ23" s="11" t="inlineStr">
         <is>
-          <t>1, 12,5,16</t>
+          <t>1, 12, 5, 16</t>
         </is>
       </c>
       <c r="AR23" s="11" t="n"/>
@@ -3184,7 +3184,7 @@
       <c r="U24" s="11" t="n"/>
       <c r="V24" s="11" t="inlineStr">
         <is>
-          <t>calamar</t>
+          <t>Calamar</t>
         </is>
       </c>
       <c r="W24" s="11" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="Z24" s="11" t="inlineStr">
         <is>
-          <t>ninos,ninas,mujeres,hombres,jovenes,adultos,etnicos,afro</t>
+          <t>Niños, Niñas, Mujeres, Hombres, Jóvenes, Adultos, Étnicos, Afro</t>
         </is>
       </c>
       <c r="AA24" s="11" t="n"/>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="AQ24" s="11" t="inlineStr">
         <is>
-          <t>1, 8,12,5</t>
+          <t>1, 8, 12, 5</t>
         </is>
       </c>
       <c r="AR24" s="11" t="n"/>
@@ -3310,7 +3310,7 @@
       <c r="U25" s="11" t="n"/>
       <c r="V25" s="11" t="inlineStr">
         <is>
-          <t>san_jose_del_guaviare</t>
+          <t>San José del Guaviare</t>
         </is>
       </c>
       <c r="W25" s="11" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="Z25" s="11" t="inlineStr">
         <is>
-          <t>ninos,ninas,mujeres,hombres,jovenes,adultos,etnicos</t>
+          <t>Niños, Niñas, Mujeres, Hombres, Jóvenes, Adultos, Étnicos</t>
         </is>
       </c>
       <c r="AA25" s="11" t="n"/>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="AQ25" s="11" t="inlineStr">
         <is>
-          <t>1,5,8,12,16</t>
+          <t>1, 5, 8, 12, 16</t>
         </is>
       </c>
       <c r="AR25" s="11" t="n"/>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>GONZALEZ OLIVEROS</t>
+          <t>Gonzalez Oliveros</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
@@ -3418,7 +3418,7 @@
       <c r="O26" s="11" t="n"/>
       <c r="P26" s="11" t="inlineStr">
         <is>
-          <t>Territorializar la política pública  de envejecimiento y vejez</t>
+          <t>Territorializar la política pública de envejecimiento y vejez</t>
         </is>
       </c>
       <c r="Q26" s="11" t="n"/>
@@ -3436,7 +3436,7 @@
       <c r="U26" s="11" t="n"/>
       <c r="V26" s="11" t="inlineStr">
         <is>
-          <t>san_jose_del_guaviare</t>
+          <t>San José del Guaviare</t>
         </is>
       </c>
       <c r="W26" s="11" t="n"/>
@@ -3448,7 +3448,7 @@
       <c r="Y26" s="11" t="n"/>
       <c r="Z26" s="11" t="inlineStr">
         <is>
-          <t>adultos</t>
+          <t>Adultos</t>
         </is>
       </c>
       <c r="AA26" s="11" t="n"/>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pablo Leon </t>
+          <t>Pablo Leon</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">​​Consultoría para la construcción de la política pública para el desarrollo económico sostenible del Guaviare que considere el potencial de la bioeconomía​ </t>
+          <t>​​Consultoría para la construcción de la política pública para el desarrollo económico sostenible del Guaviare que considere el potencial de la bioeconomía​</t>
         </is>
       </c>
       <c r="J27" s="7" t="n">
@@ -3526,7 +3526,7 @@
       <c r="O27" s="11" t="n"/>
       <c r="P27" s="11" t="inlineStr">
         <is>
-          <t>Apoyar la construcción participativa de la Política Pública de Desarrollo Económico Sostenible hacia la  Internacionalización del Guaviare, que considere el potencial de la bioeconomía. Con la política se busca brindar elementos para establecer las estrategias y rutas para mejorar el desempeño de crecimiento  económico; fomentar la protección del capital natural, el aprovechamiento sostenible de los recursos y  el control de la deforestación, así como garantizar la generación de empleo productivo.</t>
+          <t>Apoyar la construcción participativa de la Política Pública de Desarrollo Económico Sostenible hacia la Internacionalización del Guaviare, que considere el potencial de la bioeconomía. Con la política se busca brindar elementos para establecer las estrategias y rutas para mejorar el desempeño de crecimiento económico; fomentar la protección del capital natural, el aprovechamiento sostenible de los recursos y el control de la deforestación, así como garantizar la generación de empleo productivo.</t>
         </is>
       </c>
       <c r="Q27" s="11" t="n"/>
@@ -3552,7 +3552,7 @@
       <c r="Y27" s="11" t="n"/>
       <c r="Z27" s="11" t="inlineStr">
         <is>
-          <t>ninos,ninas,mujeres,hombres,jovenes,adultos,etnicos,afro,desplazados,discapacitados,reincorporados,lgbtiq</t>
+          <t>Niños, Niñas, Mujeres, Hombres, Jóvenes, Adultos, Étnicos, Afro, Desplazados, Discapacitados, Reincorporados, LGBTIQ+</t>
         </is>
       </c>
       <c r="AA27" s="11" t="n"/>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maira Alejandra Echeverry Prada </t>
+          <t>Maira Alejandra Echeverry Prada</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planta piloto de concentrados </t>
+          <t>Planta piloto de concentrados</t>
         </is>
       </c>
       <c r="J28" s="7" t="n">
@@ -3644,7 +3644,7 @@
       <c r="U28" s="11" t="n"/>
       <c r="V28" s="11" t="inlineStr">
         <is>
-          <t>san_jose_del_guaviare</t>
+          <t>San José del Guaviare</t>
         </is>
       </c>
       <c r="W28" s="11" t="inlineStr">
@@ -3660,7 +3660,7 @@
       <c r="Y28" s="11" t="n"/>
       <c r="Z28" s="11" t="inlineStr">
         <is>
-          <t>mujeres,hombres,adultos,reincorporados</t>
+          <t>Mujeres, Hombres, Adultos, Reincorporados</t>
         </is>
       </c>
       <c r="AA28" s="11" t="n"/>
@@ -3732,7 +3732,7 @@
       <c r="M29" s="11" t="n"/>
       <c r="N29" s="11" t="inlineStr">
         <is>
-          <t>Ambiental,Socioeconómico,Otro</t>
+          <t>Ambiental, Socioeconómico, Otro</t>
         </is>
       </c>
       <c r="O29" s="11" t="n"/>
@@ -3752,7 +3752,7 @@
       <c r="U29" s="11" t="n"/>
       <c r="V29" s="11" t="inlineStr">
         <is>
-          <t>San_José_Del_Guaviare</t>
+          <t>San José del Guaviare</t>
         </is>
       </c>
       <c r="W29" s="11" t="inlineStr">
@@ -3768,7 +3768,7 @@
       <c r="Y29" s="11" t="n"/>
       <c r="Z29" s="11" t="inlineStr">
         <is>
-          <t>Mujeres,Hombres,Jovenes,Adultos,Étnicos,Afro,Desplazados,LGBTIQ+</t>
+          <t>Mujeres, Hombres, Jóvenes, Adultos, Étnicos, Afro, Desplazados, LGBTIQ+</t>
         </is>
       </c>
       <c r="AA29" s="11" t="n"/>
@@ -3836,7 +3836,7 @@
       <c r="M30" s="11" t="n"/>
       <c r="N30" s="11" t="inlineStr">
         <is>
-          <t>Ambiental,Socioeconómico,Otro</t>
+          <t>Ambiental, Socioeconómico, Otro</t>
         </is>
       </c>
       <c r="O30" s="11" t="n"/>
@@ -3856,7 +3856,7 @@
       <c r="U30" s="11" t="n"/>
       <c r="V30" s="11" t="inlineStr">
         <is>
-          <t>El_Retorno,Calamar</t>
+          <t>El Retorno, Calamar</t>
         </is>
       </c>
       <c r="W30" s="11" t="inlineStr">
@@ -3872,7 +3872,7 @@
       <c r="Y30" s="11" t="n"/>
       <c r="Z30" s="11" t="inlineStr">
         <is>
-          <t>Niños,Niñas,Mujeres,Hombres,Jovenes,Adultos,Étnicos,Afro,Desplazados,Discapacitados,Reincorporados,LGBTIQ+</t>
+          <t>Niños, Niñas, Mujeres, Hombres, Jóvenes, Adultos, Étnicos, Afro, Desplazados, Discapacitados, Reincorporados, LGBTIQ+</t>
         </is>
       </c>
       <c r="AA30" s="11" t="n"/>
@@ -3940,7 +3940,7 @@
       <c r="M31" s="11" t="n"/>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>Agropecuario,Ambiental,Socioeconómico</t>
+          <t>Agropecuario, Ambiental, Socioeconómico</t>
         </is>
       </c>
       <c r="O31" s="11" t="n"/>
@@ -3960,7 +3960,7 @@
       <c r="U31" s="11" t="n"/>
       <c r="V31" s="11" t="inlineStr">
         <is>
-          <t>San_José_Del_Guaviare</t>
+          <t>San José del Guaviare</t>
         </is>
       </c>
       <c r="W31" s="11" t="inlineStr">
@@ -3976,7 +3976,7 @@
       <c r="Y31" s="11" t="n"/>
       <c r="Z31" s="11" t="inlineStr">
         <is>
-          <t>Niños,Niñas,Mujeres,Hombres,Jovenes,Adultos,Étnicos,Reincorporados</t>
+          <t>Niños, Niñas, Mujeres, Hombres, Jóvenes, Adultos, Étnicos, Reincorporados</t>
         </is>
       </c>
       <c r="AA31" s="11" t="n"/>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arando la Educación </t>
+          <t>Arando la Educación</t>
         </is>
       </c>
       <c r="J32" s="7" t="n">
@@ -4068,7 +4068,7 @@
       <c r="U32" s="11" t="n"/>
       <c r="V32" s="11" t="inlineStr">
         <is>
-          <t>San_José_Del_Guaviare</t>
+          <t>San José del Guaviare</t>
         </is>
       </c>
       <c r="W32" s="11" t="inlineStr">
@@ -4084,7 +4084,7 @@
       <c r="Y32" s="11" t="n"/>
       <c r="Z32" s="11" t="inlineStr">
         <is>
-          <t>Mujeres,Hombres,Jovenes,Adultos,Reincorporados</t>
+          <t>Mujeres, Hombres, Jóvenes, Adultos, Reincorporados</t>
         </is>
       </c>
       <c r="AA32" s="11" t="n"/>
@@ -4138,7 +4138,7 @@
       <c r="G33" s="11" t="n"/>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Onf Andina Sucursal Colombiana de Onf Internacional </t>
+          <t>Onf Andina Sucursal Colombiana de Onf Internacional</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
@@ -4176,7 +4176,7 @@
       <c r="U33" s="11" t="n"/>
       <c r="V33" s="11" t="inlineStr">
         <is>
-          <t>San_José_Del_Guaviare</t>
+          <t>San José del Guaviare</t>
         </is>
       </c>
       <c r="W33" s="11" t="inlineStr">
@@ -4192,7 +4192,7 @@
       <c r="Y33" s="11" t="n"/>
       <c r="Z33" s="11" t="inlineStr">
         <is>
-          <t>Mujeres,Hombres,Jovenes</t>
+          <t>Mujeres, Hombres, Jóvenes</t>
         </is>
       </c>
       <c r="AA33" s="11" t="n"/>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deisy Liliana Barrera </t>
+          <t>Deisy Liliana Barrera</t>
         </is>
       </c>
       <c r="C34" s="11" t="n"/>
@@ -4240,13 +4240,13 @@
       <c r="E34" s="11" t="n"/>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>BID, FCS, HUMBOLDT</t>
+          <t>BID, FCS, Humboldt</t>
         </is>
       </c>
       <c r="G34" s="11" t="n"/>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Onf Andina Sucursal Colombiana De Onf Internacional </t>
+          <t>Onf Andina Sucursal Colombiana De Onf Internacional</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
@@ -4264,7 +4264,7 @@
       <c r="M34" s="11" t="n"/>
       <c r="N34" s="11" t="inlineStr">
         <is>
-          <t>Agropecuario,Ambiental,Socioeconómico</t>
+          <t>Agropecuario, Ambiental, Socioeconómico</t>
         </is>
       </c>
       <c r="O34" s="11" t="n"/>
@@ -4284,7 +4284,7 @@
       <c r="U34" s="11" t="n"/>
       <c r="V34" s="11" t="inlineStr">
         <is>
-          <t>San_José_Del_Guaviare,El_Retorno,Calamar</t>
+          <t>San José del Guaviare, El Retorno, Calamar</t>
         </is>
       </c>
       <c r="W34" s="11" t="inlineStr">
@@ -4300,7 +4300,7 @@
       <c r="Y34" s="11" t="n"/>
       <c r="Z34" s="11" t="inlineStr">
         <is>
-          <t>Mujeres,Hombres,Jovenes,Adultos</t>
+          <t>Mujeres, Hombres, Jóvenes, Adultos</t>
         </is>
       </c>
       <c r="AA34" s="11" t="n"/>
@@ -4348,7 +4348,7 @@
       <c r="E35" s="11" t="n"/>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BID </t>
+          <t>BID</t>
         </is>
       </c>
       <c r="G35" s="11" t="n"/>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>ONSTRUCCIÓN DE LA POLÍTICA PÚBLICA PARA EL DESARROLLO ECONÓMICO SOSTENIBLE DEL GUAVIARE CON ENFOQUE DE BIOECONOMÍA</t>
+          <t>Onstrucción de la Política Pública para el Desarrollo Económico Sostenible del Guaviare con Enfoque de Bioeconomía</t>
         </is>
       </c>
       <c r="J35" s="7" t="n">
@@ -4372,7 +4372,7 @@
       <c r="M35" s="11" t="n"/>
       <c r="N35" s="11" t="inlineStr">
         <is>
-          <t>Agropecuario,Ambiental,Socioeconómico</t>
+          <t>Agropecuario, Ambiental, Socioeconómico</t>
         </is>
       </c>
       <c r="O35" s="11" t="n"/>
@@ -4392,7 +4392,7 @@
       <c r="U35" s="11" t="n"/>
       <c r="V35" s="11" t="inlineStr">
         <is>
-          <t>San_José_Del_Guaviare,El_Retorno,Calamar,Miraflores</t>
+          <t>San José del Guaviare, El Retorno, Calamar, Miraflores</t>
         </is>
       </c>
       <c r="W35" s="11" t="inlineStr">
@@ -4408,7 +4408,7 @@
       <c r="Y35" s="11" t="n"/>
       <c r="Z35" s="11" t="inlineStr">
         <is>
-          <t>Mujeres,Hombres,Adultos,Étnicos</t>
+          <t>Mujeres, Hombres, Adultos, Étnicos</t>
         </is>
       </c>
       <c r="AA35" s="11" t="n"/>
@@ -4456,7 +4456,7 @@
       <c r="E36" s="11" t="n"/>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>MINISTERIO DE LA IGUALDAD</t>
+          <t>Ministerio de la Igualdad</t>
         </is>
       </c>
       <c r="G36" s="11" t="n"/>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>TERRITORIALIZACIÓN DEL PROGRAMA NACIONAL DE CUIDADO</t>
+          <t>Territorialización del Programa Nacional de Cuidado</t>
         </is>
       </c>
       <c r="J36" s="7" t="n">
@@ -4486,7 +4486,7 @@
       <c r="O36" s="11" t="n"/>
       <c r="P36" s="11" t="inlineStr">
         <is>
-          <t>Aunar esfuerzos técnicos, operativos, administrativos y financieros orientados a apoyar la territorialización del Programa Nacional de Cuidado.   Esto en el marco del Sistema Nacional de Cuidado aprobado en el Plan Nacional de Desarrollo.</t>
+          <t>Aunar esfuerzos técnicos, operativos, administrativos y financieros orientados a apoyar la territorialización del Programa Nacional de Cuidado. Esto en el marco del Sistema Nacional de Cuidado aprobado en el Plan Nacional de Desarrollo.</t>
         </is>
       </c>
       <c r="Q36" s="11" t="n"/>
@@ -4500,7 +4500,7 @@
       <c r="U36" s="11" t="n"/>
       <c r="V36" s="11" t="inlineStr">
         <is>
-          <t>San_José_Del_Guaviare</t>
+          <t>San José del Guaviare</t>
         </is>
       </c>
       <c r="W36" s="11" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="Z36" s="11" t="inlineStr">
         <is>
-          <t>Niños,Niñas,Mujeres,Étnicos,Afro,Desplazados,Discapacitados,Reincorporados,LGBTIQ+</t>
+          <t>Niños, Niñas, Mujeres, Étnicos, Afro, Desplazados, Discapacitados, Reincorporados, LGBTIQ+</t>
         </is>
       </c>
       <c r="AA36" s="11" t="n"/>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>MILLER GONZALEZ</t>
+          <t>Miller Gonzalez</t>
         </is>
       </c>
       <c r="C37" s="11" t="n"/>
@@ -4616,7 +4616,7 @@
       <c r="U37" s="11" t="n"/>
       <c r="V37" s="11" t="inlineStr">
         <is>
-          <t>San_José_Del_Guaviare,El_Retorno,Calamar,Miraflores</t>
+          <t>San José del Guaviare, El Retorno, Calamar, Miraflores</t>
         </is>
       </c>
       <c r="W37" s="11" t="inlineStr">
@@ -4632,7 +4632,7 @@
       <c r="Y37" s="11" t="n"/>
       <c r="Z37" s="11" t="inlineStr">
         <is>
-          <t>Niños,Niñas,Mujeres,Hombres,Jovenes,Adultos,Étnicos,Afro,Desplazados,Discapacitados</t>
+          <t>Niños, Niñas, Mujeres, Hombres, Jóvenes, Adultos, Étnicos, Afro, Desplazados, Discapacitados</t>
         </is>
       </c>
       <c r="AA37" s="11" t="n"/>
@@ -4680,7 +4680,7 @@
       <c r="E38" s="11" t="n"/>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>proveniente del Programa REM  Colombia Visión Amazonía II presupuestados en el PID I, Actividad 3.2.1.1.</t>
+          <t>proveniente del Programa REM Colombia Visión Amazonía II presupuestados en el PID I, Actividad 3.2.1.1.</t>
         </is>
       </c>
       <c r="G38" s="11" t="n"/>
@@ -4704,13 +4704,13 @@
       <c r="M38" s="11" t="n"/>
       <c r="N38" s="11" t="inlineStr">
         <is>
-          <t>Agropecuario,Ambiental,Socioeconómico</t>
+          <t>Agropecuario, Ambiental, Socioeconómico</t>
         </is>
       </c>
       <c r="O38" s="11" t="n"/>
       <c r="P38" s="11" t="inlineStr">
         <is>
-          <t>implementación de  mecanismos e instrumentos de trabajo, articulando recursos técnicos, administrativos y logísticos,  para avanzar en el marco del decreto 364 de 2019...</t>
+          <t>implementación de mecanismos e instrumentos de trabajo, articulando recursos técnicos, administrativos y logísticos, para avanzar en el marco del decreto 364 de 2019...</t>
         </is>
       </c>
       <c r="Q38" s="11" t="n"/>
@@ -4740,7 +4740,7 @@
       <c r="Y38" s="11" t="n"/>
       <c r="Z38" s="11" t="inlineStr">
         <is>
-          <t>Niños,Niñas,Mujeres,Hombres,Jovenes,Adultos,Étnicos,Afro,Desplazados,Discapacitados,Reincorporados,LGBTIQ+</t>
+          <t>Niños, Niñas, Mujeres, Hombres, Jóvenes, Adultos, Étnicos, Afro, Desplazados, Discapacitados, Reincorporados, LGBTIQ+</t>
         </is>
       </c>
       <c r="AA38" s="11" t="n"/>
@@ -4780,7 +4780,7 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>VISION AMAZONIA</t>
+          <t>Vision Amazonia</t>
         </is>
       </c>
       <c r="C39" s="11" t="n"/>
@@ -4788,18 +4788,18 @@
       <c r="E39" s="11" t="n"/>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>CIENTO DIEZ MILLONES DOSCIENTOS  CINCUENTA MIL PESOS ($110.250.000) del convenio, el PID 1, Línea 3.2.1.1.</t>
+          <t>CIENTO DIEZ MILLONES DOSCIENTOS CINCUENTA MIL PESOS ($110.250.000) del convenio, el PID 1, Línea 3.2.1.1.</t>
         </is>
       </c>
       <c r="G39" s="11" t="n"/>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>PATRIMONIO NATURAL FONDO PARA LA BIODIVERSIDAD Y LAS AREAS PROTEGIDAS</t>
+          <t>Patrimonio Natural Fondo para la Biodiversidad y las Areas Protegidas</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>PLAN DE DESARROLLO DE EXTENSION AGROPECUARIA PDEA GUAVIARE</t>
+          <t>Plan de Desarrollo de Extension Agropecuaria PDEA Guaviare</t>
         </is>
       </c>
       <c r="J39" s="7" t="n">
@@ -4812,13 +4812,13 @@
       <c r="M39" s="11" t="n"/>
       <c r="N39" s="11" t="inlineStr">
         <is>
-          <t>Agropecuario,Ambiental,Socioeconómico</t>
+          <t>Agropecuario, Ambiental, Socioeconómico</t>
         </is>
       </c>
       <c r="O39" s="11" t="n"/>
       <c r="P39" s="11" t="inlineStr">
         <is>
-          <t>FORMULAR EL PDEA</t>
+          <t>Formular el PDEA</t>
         </is>
       </c>
       <c r="Q39" s="11" t="n"/>
@@ -4832,7 +4832,7 @@
       <c r="U39" s="11" t="n"/>
       <c r="V39" s="11" t="inlineStr">
         <is>
-          <t>San_José_Del_Guaviare,El_Retorno,Calamar,Miraflores</t>
+          <t>San José del Guaviare, El Retorno, Calamar, Miraflores</t>
         </is>
       </c>
       <c r="W39" s="11" t="inlineStr">
@@ -4848,7 +4848,7 @@
       <c r="Y39" s="11" t="n"/>
       <c r="Z39" s="11" t="inlineStr">
         <is>
-          <t>Mujeres,Hombres,Jovenes,Adultos,Étnicos</t>
+          <t>Mujeres, Hombres, Jóvenes, Adultos, Étnicos</t>
         </is>
       </c>
       <c r="AA39" s="11" t="n"/>
